--- a/model/data/external/infra y mov/lineas_link.xlsx
+++ b/model/data/external/infra y mov/lineas_link.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nainh\Proton Drive\nainho1306\My files\Licitacion\Plataforma prevencion Dengue\model\data\external\infra y mov\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2AF4C2-694C-4B22-B640-3AC65A85940D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462D891B-3A89-4DCA-9A86-72BFEB7933F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11235" xr2:uid="{413F5420-E2F3-4E05-9AFC-8F4BA2A86B8E}"/>
   </bookViews>
@@ -517,7 +517,7 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -541,7 +541,7 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -549,7 +549,7 @@
       <c r="A7" s="1">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -652,6 +652,9 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B15" r:id="rId1" xr:uid="{10D45D0F-1BC9-4B11-B4DF-EA6C5A00083A}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{9FDE3BF7-CF93-477F-9FAC-09213EBCC6A9}"/>
+    <hyperlink ref="B7" r:id="rId3" xr:uid="{4A88AD67-42AA-415E-93BC-2401F0978C3A}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{870F006F-5467-4ACE-BF2E-03AD6357E58C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
